--- a/Nuevo modelo/Base_Datos_Nuevo.xlsx
+++ b/Nuevo modelo/Base_Datos_Nuevo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a8e9d158fee738eb/Escritorio/01_Data science/02_Proyectos/Profesionales_personales/02_ProyectoFinanzas/Nuevo modelo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="556" documentId="11_6728A2C2DC4C5100FF52A6CD77A9E0B3E2FCC81A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{069B312F-616A-4BEB-9C90-2EFB274F6A19}"/>
+  <xr:revisionPtr revIDLastSave="586" documentId="11_6728A2C2DC4C5100FF52A6CD77A9E0B3E2FCC81A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{169780AB-4D17-4FF2-9B43-0615E9FE723E}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-4815" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FactTransaccionFinanciera" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="147">
   <si>
     <t>bbva</t>
   </si>
@@ -417,9 +417,6 @@
     <t>euro</t>
   </si>
   <si>
-    <t>Detalle</t>
-  </si>
-  <si>
     <t>MontoReal</t>
   </si>
   <si>
@@ -469,6 +466,24 @@
   </si>
   <si>
     <t>gastos variables</t>
+  </si>
+  <si>
+    <t>fondo de emergencia</t>
+  </si>
+  <si>
+    <t>completado</t>
+  </si>
+  <si>
+    <t>libertad financiera</t>
+  </si>
+  <si>
+    <t>ianctivo</t>
+  </si>
+  <si>
+    <t>TieneFacturaCFDI</t>
+  </si>
+  <si>
+    <t>CF</t>
   </si>
 </sst>
 </file>
@@ -862,11 +877,11 @@
     <col min="8" max="8" width="18.5703125" customWidth="1"/>
     <col min="9" max="9" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.140625" customWidth="1"/>
+    <col min="11" max="11" width="16.42578125" customWidth="1"/>
     <col min="16" max="16" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>77</v>
       </c>
@@ -889,7 +904,7 @@
         <v>82</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I1" s="5" t="s">
         <v>83</v>
@@ -898,7 +913,12 @@
         <v>84</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>124</v>
+        <v>145</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -947,10 +967,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B1" t="s">
         <v>137</v>
-      </c>
-      <c r="B1" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -966,7 +986,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -974,7 +994,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -1018,13 +1038,13 @@
         <v>78</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>86</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -1195,7 +1215,7 @@
         <v>102</v>
       </c>
       <c r="D1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E1" t="s">
         <v>104</v>
@@ -1204,7 +1224,7 @@
         <v>119</v>
       </c>
       <c r="G1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H1" s="6" t="s">
         <v>105</v>
@@ -1223,10 +1243,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D3" t="s">
         <v>7</v>
@@ -1308,7 +1328,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
@@ -1418,7 +1438,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C15" t="s">
         <v>6</v>
@@ -1447,7 +1467,7 @@
         <v>80</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1495,7 +1515,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1575,7 +1595,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -1652,7 +1672,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1676,7 +1696,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -1708,7 +1728,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -2031,16 +2051,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F6" t="s">
         <v>42</v>
@@ -2054,16 +2074,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="C7" t="s">
         <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F7" t="s">
         <v>42</v>
@@ -2077,22 +2097,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>141</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E8" t="s">
-        <v>39</v>
+        <v>142</v>
       </c>
       <c r="F8" t="s">
         <v>42</v>
-      </c>
-      <c r="G8">
-        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -2100,22 +2117,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>143</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E9" t="s">
-        <v>39</v>
+        <v>144</v>
       </c>
       <c r="F9" t="s">
         <v>42</v>
-      </c>
-      <c r="G9">
-        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -2185,7 +2199,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -2230,7 +2244,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C3" t="s">
         <v>44</v>
